--- a/artfynd/A 7435-2022 artfynd.xlsx
+++ b/artfynd/A 7435-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7435-2022 artfynd.xlsx
+++ b/artfynd/A 7435-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1966127</v>
+        <v>872498</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514863.1515278565</v>
+        <v>514863</v>
       </c>
       <c r="R2" t="n">
-        <v>6997608.49424127</v>
+        <v>6997608</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2010-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1966136</v>
+        <v>1157230</v>
       </c>
       <c r="B3" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515013.4972055344</v>
+        <v>514933</v>
       </c>
       <c r="R3" t="n">
-        <v>6997644.499451479</v>
+        <v>6997416</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1966126</v>
+        <v>1295879</v>
       </c>
       <c r="B4" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514932.1677834288</v>
+        <v>514933</v>
       </c>
       <c r="R4" t="n">
-        <v>6997585.269523035</v>
+        <v>6997416</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1295879</v>
+        <v>1394516</v>
       </c>
       <c r="B5" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514933.3989083268</v>
+        <v>514891</v>
       </c>
       <c r="R5" t="n">
-        <v>6997416.402654313</v>
+        <v>6997256</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,19 +1034,9 @@
           <t>2010-09-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1842960</v>
+        <v>1842728</v>
       </c>
       <c r="B6" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514969.4089019785</v>
+        <v>515035</v>
       </c>
       <c r="R6" t="n">
-        <v>6997570.953877386</v>
+        <v>6997864</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1842961</v>
+        <v>1842740</v>
       </c>
       <c r="B7" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514932.1677834288</v>
+        <v>514923</v>
       </c>
       <c r="R7" t="n">
-        <v>6997585.269523035</v>
+        <v>6997303</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>872498</v>
+        <v>1842949</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514863.1515278565</v>
+        <v>514968</v>
       </c>
       <c r="R8" t="n">
-        <v>6997608.49424127</v>
+        <v>6997361</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,19 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1842951</v>
+        <v>1842950</v>
       </c>
       <c r="B9" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514830.0267365268</v>
+        <v>514898</v>
       </c>
       <c r="R9" t="n">
-        <v>6997515.985079482</v>
+        <v>6997443</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1532,19 +1422,9 @@
           <t>2010-09-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,19 +1451,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1842950</v>
+        <v>1842951</v>
       </c>
       <c r="B10" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514897.9134754331</v>
+        <v>514830</v>
       </c>
       <c r="R10" t="n">
-        <v>6997442.951734352</v>
+        <v>6997516</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,19 +1519,9 @@
           <t>2010-09-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,19 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1842964</v>
+        <v>1842960</v>
       </c>
       <c r="B11" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515013.4972055344</v>
+        <v>514969</v>
       </c>
       <c r="R11" t="n">
-        <v>6997644.499451479</v>
+        <v>6997571</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,19 +1616,9 @@
           <t>2010-09-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2010-09-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,32 +1645,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1936932</v>
+        <v>1842961</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514863.1515278565</v>
+        <v>514932</v>
       </c>
       <c r="R12" t="n">
-        <v>6997608.49424127</v>
+        <v>6997585</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1865,22 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1893240</v>
+        <v>1842964</v>
       </c>
       <c r="B13" t="n">
-        <v>78502</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514932.1677834288</v>
+        <v>515013</v>
       </c>
       <c r="R13" t="n">
-        <v>6997585.269523035</v>
+        <v>6997644</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,22 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1842949</v>
+        <v>1893240</v>
       </c>
       <c r="B14" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514968.1119448636</v>
+        <v>514932</v>
       </c>
       <c r="R14" t="n">
-        <v>6997360.873603443</v>
+        <v>6997585</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2092,19 +1907,9 @@
           <t>2010-09-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2063978</v>
+        <v>1965527</v>
       </c>
       <c r="B15" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514932.1677834288</v>
+        <v>515035</v>
       </c>
       <c r="R15" t="n">
-        <v>6997585.269523035</v>
+        <v>6997864</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2204,19 +2004,9 @@
           <t>2010-09-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2063976</v>
+        <v>1966126</v>
       </c>
       <c r="B16" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514863.1515278565</v>
+        <v>514932</v>
       </c>
       <c r="R16" t="n">
-        <v>6997608.49424127</v>
+        <v>6997585</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2313,22 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1842740</v>
+        <v>1966127</v>
       </c>
       <c r="B17" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514922.5856330564</v>
+        <v>514863</v>
       </c>
       <c r="R17" t="n">
-        <v>6997303.16261329</v>
+        <v>6997608</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2425,22 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1555508</v>
+        <v>1966128</v>
       </c>
       <c r="B18" t="n">
-        <v>89409</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514903.24498411</v>
+        <v>514944</v>
       </c>
       <c r="R18" t="n">
-        <v>6997663.910439705</v>
+        <v>6997710</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2537,22 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1157230</v>
+        <v>1966136</v>
       </c>
       <c r="B19" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514933.3989083268</v>
+        <v>515013</v>
       </c>
       <c r="R19" t="n">
-        <v>6997416.402654313</v>
+        <v>6997644</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2649,22 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2010-09-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2688,6 +2418,491 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2063976</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ca 2,5 km N Ismundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>514863</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6997608</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2010-09-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2010-09-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2063978</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ca 2,5 km N Ismundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>514932</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6997585</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2010-09-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2010-09-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2063979</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ca 2,5 km N Ismundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>515035</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6997864</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2010-09-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2010-09-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1936932</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ca 2,5 km N Ismundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>514863</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6997608</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2010-09-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2010-09-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3039280</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ca 2,5 km N Ismundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>514944</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6997710</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2010-09-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2010-09-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7435-2022 artfynd.xlsx
+++ b/artfynd/A 7435-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/872498</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1157230</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1295879</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1394516</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842728</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842740</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842949</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842950</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842951</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842960</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842961</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1842964</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893240</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965527</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1966126</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1966127</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1966128</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1966136</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2063976</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2063978</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2063979</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1936932</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,8 +3018,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3039280</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>